--- a/microgridspy/results/Sizing Results.xlsx
+++ b/microgridspy/results/Sizing Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Component</t>
   </si>
@@ -23,6 +23,9 @@
   </si>
   <si>
     <t>Step 1</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
   <si>
     <t>Solar PV (kW)</t>
@@ -389,10 +392,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -402,38 +405,50 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>5836</v>
+        <v>47.7203232652036</v>
+      </c>
+      <c r="D2">
+        <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <v>1118</v>
+        <v>4.038835721932195</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4">
-        <v>18600</v>
+        <v>167.1983865576615</v>
+      </c>
+      <c r="D4">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/microgridspy/results/Sizing Results.xlsx
+++ b/microgridspy/results/Sizing Results.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Component</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>Diesel Generator (kW)</t>
+  </si>
+  <si>
+    <t>Battery (kWh)</t>
   </si>
 </sst>
 </file>
@@ -389,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -414,10 +417,10 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>27</v>
+        <v>425</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>425</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -428,10 +431,24 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>23</v>
+        <v>179</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>2830</v>
+      </c>
+      <c r="D4">
+        <v>2830</v>
       </c>
     </row>
   </sheetData>
